--- a/artfynd/A 27695-2025 artfynd.xlsx
+++ b/artfynd/A 27695-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136368416</v>
       </c>
       <c r="B2" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136368521</v>
       </c>
       <c r="B3" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136368606</v>
       </c>
       <c r="B4" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 27695-2025 artfynd.xlsx
+++ b/artfynd/A 27695-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136368416</v>
       </c>
       <c r="B2" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136368521</v>
       </c>
       <c r="B3" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136368606</v>
       </c>
       <c r="B4" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 27695-2025 artfynd.xlsx
+++ b/artfynd/A 27695-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136368416</v>
       </c>
       <c r="B2" t="n">
-        <v>93404</v>
+        <v>93409</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136368521</v>
       </c>
       <c r="B3" t="n">
-        <v>93404</v>
+        <v>93409</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136368606</v>
       </c>
       <c r="B4" t="n">
-        <v>93404</v>
+        <v>93409</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>136368444</v>
       </c>
       <c r="B5" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>136368482</v>
       </c>
       <c r="B6" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>136368467</v>
       </c>
       <c r="B7" t="n">
-        <v>79497</v>
+        <v>79499</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1319,7 +1319,7 @@
         <v>136368572</v>
       </c>
       <c r="B8" t="n">
-        <v>79497</v>
+        <v>79499</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1425,7 +1425,7 @@
         <v>136368590</v>
       </c>
       <c r="B9" t="n">
-        <v>79497</v>
+        <v>79499</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 27695-2025 artfynd.xlsx
+++ b/artfynd/A 27695-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136368416</v>
       </c>
       <c r="B2" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136368521</v>
       </c>
       <c r="B3" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136368606</v>
       </c>
       <c r="B4" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 27695-2025 artfynd.xlsx
+++ b/artfynd/A 27695-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136368416</v>
       </c>
       <c r="B2" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136368521</v>
       </c>
       <c r="B3" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136368606</v>
       </c>
       <c r="B4" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>136368444</v>
       </c>
       <c r="B5" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>136368482</v>
       </c>
       <c r="B6" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>136368467</v>
       </c>
       <c r="B7" t="n">
-        <v>79499</v>
+        <v>79503</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1319,7 +1319,7 @@
         <v>136368572</v>
       </c>
       <c r="B8" t="n">
-        <v>79499</v>
+        <v>79503</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1425,7 +1425,7 @@
         <v>136368590</v>
       </c>
       <c r="B9" t="n">
-        <v>79499</v>
+        <v>79503</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 27695-2025 artfynd.xlsx
+++ b/artfynd/A 27695-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136368416</v>
       </c>
       <c r="B2" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136368521</v>
       </c>
       <c r="B3" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136368606</v>
       </c>
       <c r="B4" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>136368444</v>
       </c>
       <c r="B5" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>136368482</v>
       </c>
       <c r="B6" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>136368467</v>
       </c>
       <c r="B7" t="n">
-        <v>79503</v>
+        <v>79505</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1319,7 +1319,7 @@
         <v>136368572</v>
       </c>
       <c r="B8" t="n">
-        <v>79503</v>
+        <v>79505</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1425,7 +1425,7 @@
         <v>136368590</v>
       </c>
       <c r="B9" t="n">
-        <v>79503</v>
+        <v>79505</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
